--- a/data/gravel/Massi Incanto 2025.xlsx
+++ b/data/gravel/Massi Incanto 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CDED11-6653-BD45-B034-8BC2539D8797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A851620D-AFBC-D345-A1A5-A2ACD3F39DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4240" yWindow="2620" windowWidth="24560" windowHeight="14280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -345,6 +345,9 @@
   </si>
   <si>
     <t>a8:h30</t>
+  </si>
+  <si>
+    <t>https://masibikes.com/cdn/shop/files/2024-Masi-Incanto-Rival.jpg?v=1713974014&amp;width=1346</t>
   </si>
 </sst>
 </file>
@@ -731,6 +734,11 @@
         <v>98</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>104</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
